--- a/artfynd/A 33581-2026 artfynd.xlsx
+++ b/artfynd/A 33581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888250</v>
       </c>
       <c r="B2" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135888249</v>
       </c>
       <c r="B3" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33581-2026 artfynd.xlsx
+++ b/artfynd/A 33581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888250</v>
       </c>
       <c r="B2" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135888249</v>
       </c>
       <c r="B3" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135888246</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>135888247</v>
       </c>
       <c r="B5" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33581-2026 artfynd.xlsx
+++ b/artfynd/A 33581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888250</v>
       </c>
       <c r="B2" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135888249</v>
       </c>
       <c r="B3" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135888246</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>135888247</v>
       </c>
       <c r="B5" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33581-2026 artfynd.xlsx
+++ b/artfynd/A 33581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888250</v>
       </c>
       <c r="B2" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135888249</v>
       </c>
       <c r="B3" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33581-2026 artfynd.xlsx
+++ b/artfynd/A 33581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888250</v>
       </c>
       <c r="B2" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135888249</v>
       </c>
       <c r="B3" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135888246</v>
       </c>
       <c r="B4" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>135888247</v>
       </c>
       <c r="B5" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33581-2026 artfynd.xlsx
+++ b/artfynd/A 33581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888250</v>
       </c>
       <c r="B2" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135888249</v>
       </c>
       <c r="B3" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135888246</v>
       </c>
       <c r="B4" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>135888247</v>
       </c>
       <c r="B5" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33581-2026 artfynd.xlsx
+++ b/artfynd/A 33581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888250</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135888249</v>
       </c>
       <c r="B3" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135888246</v>
       </c>
       <c r="B4" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>135888247</v>
       </c>
       <c r="B5" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
